--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI4"/>
+  <dimension ref="A1:BI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,27 +748,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="BI2" s="3" t="n">
-        <v>46100.875</v>
+        <v>46100.33333333334</v>
       </c>
     </row>
     <row r="3">
@@ -945,27 +945,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46100.875</v>
+        <v>46100.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -1142,27 +1142,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1330,7 +1330,3947 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
+        <v>46100.45833333334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Azerbaijan Premyer Liqası</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sabah</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sumqayıt</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="3" t="n">
+        <v>46100.51041666666</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Iran Persian Gulf Pro League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Paykan</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Foolad</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="3" t="n">
+        <v>46100.54166666666</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Iran Persian Gulf Pro League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Esteghlal</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sepahan</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="3" t="n">
+        <v>46100.54166666666</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Iran Persian Gulf Pro League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aluminium Arak</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Chadormalu SC</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="3" t="n">
+        <v>46100.54166666666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bulgaria First League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Spartak Varna</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="3" t="n">
+        <v>46100.54166666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Turkey Süper Lig</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Konyaspor</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gençlerbirliği</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="3" t="n">
+        <v>46100.58333333334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Turkey Süper Lig</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Beşiktaş</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kasımpaşa</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="3" t="n">
+        <v>46100.58333333334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Quevilly Rouen</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="3" t="n">
+        <v>46100.625</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Dinamo Bucureşti</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CS U Craiova</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" s="3" t="n">
+        <v>46100.64583333334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SD Aucas</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Técnico Universitario</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" s="3" t="n">
+        <v>46100.66666666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mushuc Runa SC</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" s="3" t="n">
+        <v>46100.77083333334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" s="3" t="n">
+        <v>46100.79166666666</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>New York City II</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toronto II</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" s="3" t="n">
+        <v>46100.83333333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" s="3" t="n">
+        <v>46100.83333333334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Nasaf</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Termez Surkhon</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" s="3" t="n">
         <v>46100.875</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CSD Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="3" t="n">
+        <v>46100.875</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sogdiana</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pakhtakor</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" s="3" t="n">
+        <v>46100.875</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Neftchi</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lokomotiv</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" s="3" t="n">
+        <v>46100.875</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Austria 2. Liga</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Schwarz-Weiß Bregenz</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SV Stripfing Weiden</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" s="3" t="n">
+        <v>46100.875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" s="3" t="n">
+        <v>46100.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3807,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3807,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3807,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI24"/>
+  <dimension ref="A1:BI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,27 +945,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46100.41666666666</v>
+        <v>46100.33333333334</v>
       </c>
     </row>
     <row r="4">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46100.45833333334</v>
+        <v>46100.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -1339,27 +1339,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46100.51041666666</v>
+        <v>46100.42708333334</v>
       </c>
     </row>
     <row r="6">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46100.54166666666</v>
+        <v>46100.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46100.54166666666</v>
+        <v>46100.51041666666</v>
       </c>
     </row>
     <row r="8">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46100.58333333334</v>
+        <v>46100.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46100.58333333334</v>
+        <v>46100.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46100.625</v>
+        <v>46100.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46100.64583333334</v>
+        <v>46100.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -3112,27 +3112,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46100.66666666666</v>
+        <v>46100.625</v>
       </c>
     </row>
     <row r="15">
@@ -3309,27 +3309,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46100.77083333334</v>
+        <v>46100.64583333334</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46100.79166666666</v>
+        <v>46100.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -3703,27 +3703,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3807,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46100.83333333334</v>
+        <v>46100.72916666666</v>
       </c>
     </row>
     <row r="18">
@@ -3900,27 +3900,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46100.83333333334</v>
+        <v>46100.72916666666</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46100.875</v>
+        <v>46100.72916666666</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46100.875</v>
+        <v>46100.77083333334</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46100.875</v>
+        <v>46100.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46100.875</v>
+        <v>46100.83333333334</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4989,10 +4989,10 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46100.875</v>
+        <v>46100.83333333334</v>
       </c>
     </row>
     <row r="24">
@@ -5082,27 +5082,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,145 +5131,539 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" s="3" t="n">
+        <v>46100.875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CSD Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" s="3" t="n">
+        <v>46100.875</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
         <v>3</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>3.25</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>2.3</v>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
         <v>2.15</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AF26" t="n">
         <v>1.62</v>
       </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI24" s="3" t="n">
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="3" t="n">
         <v>46100.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4989,10 +4989,10 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4989,10 +4989,10 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,17 +2176,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4989,10 +4989,10 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,17 +2176,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,17 +2373,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,17 +1979,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,17 +2373,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3174,70 +3174,70 @@
         <v>1.72</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="R4" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="S4" t="n">
         <v>2.5</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,17 +1979,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,137 +2373,137 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>8.91</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>5.13</v>
+        <v>4.53</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,137 +2373,137 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>4.53</v>
+        <v>4.33</v>
       </c>
       <c r="S16" t="n">
         <v>2.3</v>
@@ -3637,34 +3637,34 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3682,7 +3682,7 @@
         <v>3.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF16" t="n">
         <v>1.13</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4553,124 +4553,124 @@
         <v>4.75</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,137 +2373,137 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -3589,13 +3589,13 @@
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
         <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
         <v>1.36</v>
@@ -3610,13 +3610,13 @@
         <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AI16" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.03</v>
@@ -3637,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.55</v>
@@ -3646,13 +3646,13 @@
         <v>2.21</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="AV16" t="n">
         <v>2.26</v>
@@ -3661,16 +3661,16 @@
         <v>1.78</v>
       </c>
       <c r="AX16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>1.46</v>
       </c>
-      <c r="AY16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB16" t="n">
         <v>1.3</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="S21" t="n">
         <v>2.19</v>
@@ -4568,7 +4568,7 @@
         <v>3.1</v>
       </c>
       <c r="X21" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="Y21" t="n">
         <v>1.44</v>
@@ -4592,7 +4592,7 @@
         <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AG21" t="n">
         <v>2.85</v>
@@ -4604,7 +4604,7 @@
         <v>5.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK21" t="n">
         <v>1.75</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="S23" t="n">
         <v>1.53</v>
@@ -4956,52 +4956,52 @@
         <v>9.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="X23" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB23" t="n">
         <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AL23" t="n">
         <v>1.67</v>
@@ -5010,7 +5010,7 @@
         <v>1.11</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,16 +5052,16 @@
         <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BF23" t="n">
         <v>1.25</v>
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
         <v>2.3</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,137 +1979,137 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,137 +2373,137 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="X4" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.8</v>
+        <v>6.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,13 +1309,13 @@
         <v>2.63</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="BE4" t="n">
         <v>1.67</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,137 +1979,137 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2771,106 +2771,106 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.24</v>
+        <v>5.15</v>
       </c>
       <c r="R12" t="n">
-        <v>8.91</v>
+        <v>7.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V12" t="n">
         <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="X12" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="Z12" t="n">
         <v>4.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
         <v>2.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.44</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AT12" t="n">
         <v>2.7</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AV12" t="n">
         <v>2.55</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AX12" t="n">
         <v>1.62</v>
@@ -2879,25 +2879,25 @@
         <v>1.38</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="S13" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="X13" t="n">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AM13" t="n">
         <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3049,13 +3049,13 @@
         <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AT13" t="n">
         <v>3.55</v>
@@ -3064,13 +3064,13 @@
         <v>2.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AY13" t="n">
         <v>1.24</v>
@@ -3082,19 +3082,19 @@
         <v>2.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
         <v>1.72</v>
@@ -3204,22 +3204,22 @@
         <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.5</v>
+        <v>4.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" t="n">
         <v>9.5</v>
@@ -3237,7 +3237,7 @@
         <v>1.95</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S15" t="n">
-        <v>3.24</v>
+        <v>3.52</v>
       </c>
       <c r="T15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U15" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="V15" t="n">
         <v>1.45</v>
@@ -3386,55 +3386,55 @@
         <v>2.53</v>
       </c>
       <c r="X15" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB15" t="n">
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AI15" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK15" t="n">
         <v>1.83</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>2.18</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,83 +5131,83 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,83 +5328,83 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,137 +1979,137 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.15</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>7.5</v>
+        <v>4.33</v>
       </c>
       <c r="S12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.73</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AG12" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.8</v>
+        <v>5.64</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="Q13" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
         <v>3.5</v>
       </c>
-      <c r="R13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AV13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,83 +5131,83 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,83 +5328,83 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1195,22 +1195,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="R4" t="n">
         <v>3.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>4.3</v>
+        <v>4.51</v>
       </c>
       <c r="V4" t="n">
         <v>1.38</v>
@@ -1219,7 +1219,7 @@
         <v>2.81</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
         <v>1.4</v>
@@ -1228,7 +1228,7 @@
         <v>6.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AB4" t="n">
         <v>1.05</v>
@@ -1243,7 +1243,7 @@
         <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
         <v>3.2</v>
@@ -1267,7 +1267,7 @@
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,13 +1309,13 @@
         <v>2.63</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
         <v>2.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="BE4" t="n">
         <v>1.67</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,137 +1979,137 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>10.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.37</v>
       </c>
       <c r="Q12" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU12" t="n">
         <v>3.5</v>
       </c>
-      <c r="R12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AV12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC12" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="BD12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.63</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.15</v>
+        <v>3.57</v>
       </c>
       <c r="R13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z13" t="n">
         <v>7.5</v>
       </c>
-      <c r="S13" t="n">
+      <c r="AA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.73</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AG13" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q15" t="n">
         <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="S15" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="U15" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="X15" t="n">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB15" t="n">
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AJ15" t="n">
         <v>1.03</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
         <v>1.83</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>2.18</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>10.54</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.24</v>
+        <v>3.57</v>
       </c>
       <c r="R12" t="n">
-        <v>7.25</v>
+        <v>4.2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>5.42</v>
+        <v>4.6</v>
       </c>
       <c r="V12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.25</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AI12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT12" t="n">
         <v>3.55</v>
       </c>
-      <c r="X12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="AU12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.27</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>5.24</v>
       </c>
       <c r="R13" t="n">
-        <v>4.2</v>
+        <v>7.25</v>
       </c>
       <c r="S13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.3</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AG13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN13" t="n">
         <v>3.1</v>
       </c>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK13" t="n">
+      <c r="AQ13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN13" t="n">
+      <c r="BD13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.63</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3562,10 +3562,10 @@
         <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="R16" t="n">
-        <v>4.33</v>
+        <v>4.53</v>
       </c>
       <c r="S16" t="n">
         <v>2.3</v>
@@ -3610,7 +3610,7 @@
         <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="AH16" t="n">
         <v>1.19</v>
@@ -3631,13 +3631,13 @@
         <v>1.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.55</v>
@@ -3646,13 +3646,13 @@
         <v>2.21</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.6</v>
+        <v>3.38</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="AV16" t="n">
         <v>2.26</v>
@@ -3661,10 +3661,10 @@
         <v>1.78</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AZ16" t="n">
         <v>1.46</v>
@@ -3679,7 +3679,7 @@
         <v>2.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="BE16" t="n">
         <v>1.55</v>
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD20" t="n">
         <v>3.25</v>
       </c>
-      <c r="R20" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,16 +4544,16 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="T21" t="n">
         <v>2.3</v>
@@ -4562,16 +4562,16 @@
         <v>4.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="X21" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z21" t="n">
         <v>6.35</v>
@@ -4586,25 +4586,25 @@
         <v>1.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AE21" t="n">
         <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AH21" t="n">
         <v>1.33</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK21" t="n">
         <v>1.75</v>
@@ -4616,49 +4616,49 @@
         <v>1.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC21" t="n">
         <v>2.05</v>
@@ -4670,7 +4670,7 @@
         <v>1.73</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,83 +5328,83 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
         <v>2.3</v>
@@ -5565,7 +5565,7 @@
         <v>1.01</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AC26" t="n">
         <v>1.36</v>
@@ -5580,16 +5580,16 @@
         <v>1.65</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" t="n">
         <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
         <v>1.85</v>
@@ -5598,49 +5598,49 @@
         <v>1.85</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BB26" t="n">
         <v>1.3</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -840,22 +840,22 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -1195,34 +1195,34 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
         <v>3.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>4.51</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>2.81</v>
+        <v>3.07</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z4" t="n">
         <v>6.65</v>
@@ -1231,31 +1231,31 @@
         <v>1.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AF4" t="n">
         <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI4" t="n">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
         <v>1.73</v>
@@ -1264,40 +1264,40 @@
         <v>2</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AS4" t="n">
         <v>2.65</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.55</v>
+        <v>3.07</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="AW4" t="n">
         <v>1.66</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AY4" t="n">
         <v>1.24</v>
@@ -1312,16 +1312,16 @@
         <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1786,22 +1786,22 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1825,22 +1825,22 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2574,40 +2574,40 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>10.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.75</v>
+        <v>5.84</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W11" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="X11" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
         <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AB11" t="n">
         <v>1.03</v>
@@ -2622,28 +2622,28 @@
         <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AL11" t="n">
         <v>1.7</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AN11" t="n">
         <v>1.04</v>
@@ -2688,10 +2688,10 @@
         <v>1.06</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="BD11" t="n">
         <v>4.6</v>
@@ -2700,7 +2700,7 @@
         <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="X12" t="n">
         <v>3.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA12" t="n">
         <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK12" t="n">
         <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2888,16 +2888,16 @@
         <v>1.29</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="BD12" t="n">
         <v>3.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,28 +2968,28 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.24</v>
+        <v>4.8</v>
       </c>
       <c r="R13" t="n">
-        <v>7.25</v>
+        <v>7.9</v>
       </c>
       <c r="S13" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="U13" t="n">
-        <v>5.42</v>
+        <v>5.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="X13" t="n">
         <v>2.32</v>
@@ -2998,46 +2998,46 @@
         <v>1.54</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AE13" t="n">
         <v>1.53</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AN13" t="n">
         <v>3.1</v>
@@ -3082,19 +3082,19 @@
         <v>4.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BC13" t="n">
         <v>1.85</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
         <v>1.85</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,52 +3165,52 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="T14" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="X14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="AF14" t="n">
         <v>1.57</v>
@@ -3219,25 +3219,25 @@
         <v>4.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AI14" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.01</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,16 +3279,16 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BF14" t="n">
         <v>1.08</v>
@@ -3362,37 +3362,37 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="S15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="X15" t="n">
         <v>3.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.95</v>
       </c>
       <c r="Y15" t="n">
         <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA15" t="n">
         <v>1.03</v>
@@ -3401,40 +3401,40 @@
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
         <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.09</v>
+        <v>3.82</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>2.18</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3571,19 +3571,19 @@
         <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="V16" t="n">
         <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="X16" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
@@ -3595,76 +3595,76 @@
         <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
         <v>7.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN16" t="n">
         <v>1.91</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AW16" t="n">
         <v>1.75</v>
       </c>
-      <c r="AM16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AX16" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AZ16" t="n">
         <v>1.46</v>
@@ -3673,19 +3673,19 @@
         <v>3.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC16" t="n">
         <v>2.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="V20" t="n">
         <v>1.43</v>
@@ -4371,7 +4371,7 @@
         <v>2.53</v>
       </c>
       <c r="X20" t="n">
-        <v>2.91</v>
+        <v>3.07</v>
       </c>
       <c r="Y20" t="n">
         <v>1.33</v>
@@ -4398,28 +4398,28 @@
         <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AH20" t="n">
         <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BC20" t="n">
         <v>2.25</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,19 +4544,19 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q21" t="n">
         <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="S21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.3</v>
       </c>
       <c r="U21" t="n">
         <v>4.5</v>
@@ -4568,16 +4568,16 @@
         <v>3.04</v>
       </c>
       <c r="X21" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.35</v>
+        <v>5.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB21" t="n">
         <v>1.04</v>
@@ -4589,31 +4589,31 @@
         <v>3.7</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AH21" t="n">
         <v>1.33</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.08</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL21" t="n">
         <v>1.95</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AN21" t="n">
         <v>2.1</v>
@@ -4658,16 +4658,16 @@
         <v>3</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BF21" t="n">
         <v>1.17</v>
@@ -4938,22 +4938,22 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="R23" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="S23" t="n">
         <v>1.53</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="U23" t="n">
-        <v>9.5</v>
+        <v>11.31</v>
       </c>
       <c r="V23" t="n">
         <v>1.23</v>
@@ -4962,13 +4962,13 @@
         <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
         <v>1.14</v>
@@ -4980,37 +4980,37 @@
         <v>1.16</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.6</v>
+        <v>4.65</v>
       </c>
       <c r="AE23" t="n">
         <v>1.49</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AN23" t="n">
-        <v>5.14</v>
+        <v>4.4</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5055,13 +5055,13 @@
         <v>1.13</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="BF23" t="n">
         <v>1.28</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5532,13 +5532,13 @@
         <v>3.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
         <v>2.05</v>
@@ -5547,25 +5547,25 @@
         <v>2.9</v>
       </c>
       <c r="V26" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
         <v>2.56</v>
       </c>
       <c r="X26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
         <v>1.36</v>
@@ -5574,10 +5574,10 @@
         <v>2.88</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG26" t="n">
         <v>4</v>
@@ -5589,7 +5589,7 @@
         <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK26" t="n">
         <v>1.85</v>
@@ -5655,7 +5655,7 @@
         <v>1.53</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>11.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>11.31</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5332,28 +5332,28 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="Q25" t="n">
         <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="S25" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="V25" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="X25" t="n">
         <v>3.15</v>
@@ -5362,10 +5362,10 @@
         <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AB25" t="n">
         <v>1.06</v>
@@ -5374,16 +5374,16 @@
         <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AH25" t="n">
         <v>1.2</v>
@@ -5395,16 +5395,16 @@
         <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5440,25 +5440,25 @@
         <v>1.41</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC25" t="n">
         <v>2.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,137 +2373,137 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>10.54</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3559,19 +3559,19 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.53</v>
+        <v>4.4</v>
       </c>
       <c r="S16" t="n">
         <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U16" t="n">
         <v>4.75</v>
@@ -3619,16 +3619,16 @@
         <v>7.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AN16" t="n">
         <v>1.91</v>
@@ -3637,34 +3637,34 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.48</v>
+        <v>3.32</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.04</v>
+        <v>3.17</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AZ16" t="n">
         <v>1.46</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
         <v>3.5</v>
@@ -4425,40 +4425,40 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="BB20" t="n">
         <v>1.24</v>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
         <v>4.6</v>
@@ -4556,7 +4556,7 @@
         <v>2.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
         <v>4.5</v>
@@ -4565,7 +4565,7 @@
         <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="X21" t="n">
         <v>2.65</v>
@@ -4583,31 +4583,31 @@
         <v>1.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.08</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL21" t="n">
         <v>1.95</v>
@@ -4661,16 +4661,16 @@
         <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="BD21" t="n">
         <v>4.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S22" t="n">
         <v>1.53</v>
@@ -4861,7 +4861,7 @@
         <v>1.77</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="BE22" t="n">
         <v>1.98</v>
@@ -5332,22 +5332,22 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.53</v>
+        <v>3.35</v>
       </c>
       <c r="Q25" t="n">
         <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="S25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U25" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="V25" t="n">
         <v>1.4</v>
@@ -5374,16 +5374,16 @@
         <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AE25" t="n">
         <v>2.15</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
         <v>1.2</v>
@@ -5395,16 +5395,16 @@
         <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5422,10 +5422,10 @@
         <v>2.08</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="AV25" t="n">
         <v>2.6</v>
@@ -5437,7 +5437,7 @@
         <v>1.64</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="AZ25" t="n">
         <v>3.05</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S26" t="n">
         <v>3.6</v>
@@ -5562,7 +5562,7 @@
         <v>7.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB26" t="n">
         <v>1.02</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -840,22 +840,22 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1037,22 +1037,22 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
         <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="S16" t="n">
         <v>2.3</v>
@@ -3637,34 +3637,34 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY16" t="n">
         <v>1.27</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.24</v>
       </c>
       <c r="AZ16" t="n">
         <v>1.46</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4350,7 +4350,7 @@
         <v>1.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
         <v>3.5</v>
@@ -4392,7 +4392,7 @@
         <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
         <v>1.67</v>
@@ -4455,10 +4455,10 @@
         <v>1.27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.62</v>
+        <v>2.77</v>
       </c>
       <c r="BB20" t="n">
         <v>1.24</v>
@@ -4544,19 +4544,19 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="S21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.25</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.3</v>
       </c>
       <c r="U21" t="n">
         <v>4.5</v>
@@ -4565,58 +4565,58 @@
         <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="X21" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="Y21" t="n">
         <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA21" t="n">
         <v>1.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL21" t="n">
         <v>1.95</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4625,25 +4625,25 @@
         <v>1.33</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AR21" t="n">
         <v>1.94</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AU21" t="n">
         <v>3</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AX21" t="n">
         <v>1.46</v>
@@ -4655,22 +4655,22 @@
         <v>1.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="BD21" t="n">
         <v>4.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="R22" t="n">
         <v>12</v>
@@ -4795,13 +4795,13 @@
         <v>2.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
         <v>2.1</v>
@@ -4861,7 +4861,7 @@
         <v>1.77</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="BE22" t="n">
         <v>1.98</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5538,31 +5538,31 @@
         <v>2.3</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
         <v>2.05</v>
       </c>
       <c r="U26" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V26" t="n">
         <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AB26" t="n">
         <v>1.02</v>
@@ -5574,13 +5574,13 @@
         <v>2.88</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG26" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="AH26" t="n">
         <v>1.22</v>
@@ -5592,7 +5592,7 @@
         <v>1.02</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL26" t="n">
         <v>1.85</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -840,22 +840,22 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1037,22 +1037,22 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,137 +1979,137 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,137 +2373,137 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>10.54</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -3168,25 +3168,25 @@
         <v>5.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="S14" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="U14" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="X14" t="n">
         <v>3.25</v>
@@ -3201,25 +3201,25 @@
         <v>1.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="AF14" t="n">
         <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.37</v>
+        <v>3.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" t="n">
         <v>8.6</v>
@@ -3228,13 +3228,13 @@
         <v>1.01</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AN14" t="n">
         <v>1.1</v>
@@ -3279,16 +3279,16 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BC14" t="n">
         <v>2.44</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BF14" t="n">
         <v>1.08</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>3.27</v>
       </c>
       <c r="R15" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="S15" t="n">
         <v>2.9</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>11.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>11.31</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -840,22 +840,22 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1037,22 +1037,22 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
         <v>3.5</v>
@@ -1204,7 +1204,7 @@
         <v>3.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="T4" t="n">
         <v>2.2</v>
@@ -1216,7 +1216,7 @@
         <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="X4" t="n">
         <v>2.73</v>
@@ -1243,16 +1243,16 @@
         <v>1.92</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AH4" t="n">
         <v>1.35</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.06</v>
+        <v>6.12</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.07</v>
@@ -1267,7 +1267,7 @@
         <v>1.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1321,7 +1321,7 @@
         <v>1.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="R12" t="n">
+        <v>8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI12" t="n">
         <v>4.33</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AJ12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AQ12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC12" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="BD12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>7.9</v>
+        <v>4.52</v>
       </c>
       <c r="S13" t="n">
-        <v>1.73</v>
+        <v>2.43</v>
       </c>
       <c r="T13" t="n">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>5.9</v>
+        <v>4.95</v>
       </c>
       <c r="V13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.28</v>
       </c>
-      <c r="W13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AD13" t="n">
-        <v>4.3</v>
+        <v>3.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.33</v>
+        <v>5.6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -840,22 +840,22 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1037,22 +1037,22 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>11.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>11.31</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,137 +1979,137 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.28</v>
       </c>
-      <c r="W12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AD12" t="n">
-        <v>4.3</v>
+        <v>3.12</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.33</v>
+        <v>5.6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="Q13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W13" t="n">
         <v>3.5</v>
       </c>
-      <c r="R13" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.69</v>
-      </c>
       <c r="X13" t="n">
-        <v>3.02</v>
+        <v>2.32</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK13" t="n">
+      <c r="AQ13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="BD13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="Q12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W12" t="n">
         <v>3.5</v>
       </c>
-      <c r="R12" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.69</v>
-      </c>
       <c r="X12" t="n">
-        <v>3.02</v>
+        <v>2.32</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AQ12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC12" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="BD12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>8</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.28</v>
       </c>
-      <c r="W13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AD13" t="n">
-        <v>4.3</v>
+        <v>3.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.33</v>
+        <v>5.6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="U15" t="n">
-        <v>3.34</v>
+        <v>3.46</v>
       </c>
       <c r="V15" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="X15" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="Y15" t="n">
         <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM15" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM15" t="n">
+      <c r="AN15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.45</v>
       </c>
-      <c r="AN15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.28</v>
+        <v>2.99</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,19 +3559,19 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q16" t="n">
         <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.3</v>
+        <v>4.53</v>
       </c>
       <c r="S16" t="n">
         <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
         <v>4.75</v>
@@ -3598,10 +3598,10 @@
         <v>1.07</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AE16" t="n">
         <v>2.12</v>
@@ -3616,10 +3616,10 @@
         <v>1.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK16" t="n">
         <v>1.95</v>
@@ -3628,7 +3628,7 @@
         <v>1.72</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AN16" t="n">
         <v>1.91</v>
@@ -3667,7 +3667,7 @@
         <v>1.27</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BA16" t="n">
         <v>3.1</v>
@@ -3676,7 +3676,7 @@
         <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BD16" t="n">
         <v>3.1</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
         <v>3.3</v>
@@ -4356,13 +4356,13 @@
         <v>3.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
         <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="V20" t="n">
         <v>1.43</v>
@@ -4410,55 +4410,55 @@
         <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AM20" t="n">
         <v>1.3</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.16</v>
+        <v>3.48</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.77</v>
+        <v>3.62</v>
       </c>
       <c r="BB20" t="n">
         <v>1.24</v>
@@ -4544,67 +4544,67 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="X21" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.25</v>
+        <v>7.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AE21" t="n">
         <v>1.98</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" t="n">
         <v>6.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
         <v>1.77</v>
@@ -4613,64 +4613,64 @@
         <v>1.95</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AN21" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AU21" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="BB21" t="n">
         <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>1.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="R22" t="n">
         <v>12</v>
       </c>
       <c r="S22" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T22" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="U22" t="n">
         <v>11.31</v>
@@ -4765,16 +4765,16 @@
         <v>3.58</v>
       </c>
       <c r="X22" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB22" t="n">
         <v>1.02</v>
@@ -4783,7 +4783,7 @@
         <v>1.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AE22" t="n">
         <v>1.49</v>
@@ -4792,22 +4792,22 @@
         <v>2.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
         <v>2.1</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AM22" t="n">
         <v>1.1</v>
@@ -4819,13 +4819,13 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AS22" t="n">
         <v>1.91</v>
@@ -4834,13 +4834,13 @@
         <v>2.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.1</v>
+        <v>4.34</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AX22" t="n">
         <v>1.77</v>
@@ -4849,7 +4849,7 @@
         <v>1.49</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="BA22" t="n">
         <v>6.5</v>
@@ -4858,16 +4858,16 @@
         <v>1.13</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BD22" t="n">
         <v>4.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,16 +5529,16 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T26" t="n">
         <v>2.05</v>
@@ -5574,34 +5574,34 @@
         <v>2.88</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.02</v>
       </c>
       <c r="AK26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL26" t="n">
         <v>1.87</v>
       </c>
-      <c r="AL26" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AM26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5610,31 +5610,31 @@
         <v>1.23</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AW26" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AX26" t="n">
         <v>1.63</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AZ26" t="n">
         <v>2.02</v>
@@ -5655,7 +5655,7 @@
         <v>1.53</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>6.82</v>
+        <v>6.6</v>
       </c>
       <c r="Q2" t="n">
         <v>3.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1195,37 +1195,37 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
         <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
         <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="X4" t="n">
         <v>2.73</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.65</v>
+        <v>6.55</v>
       </c>
       <c r="AA4" t="n">
         <v>1.09</v>
@@ -1240,22 +1240,22 @@
         <v>3.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.12</v>
+        <v>5.98</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
         <v>1.73</v>
@@ -1273,34 +1273,34 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AS4" t="n">
         <v>2.65</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.07</v>
+        <v>3.55</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AW4" t="n">
         <v>1.66</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.61</v>
@@ -1309,16 +1309,16 @@
         <v>2.63</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BD4" t="n">
         <v>3.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BF4" t="n">
         <v>1.17</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AN7" t="n">
         <v>2.05</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.28</v>
-      </c>
       <c r="W12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG12" t="n">
         <v>3.5</v>
       </c>
-      <c r="X12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW13" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK13" t="n">
+      <c r="AX13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="BD13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,19 +3165,19 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>5.15</v>
+        <v>4.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="T14" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
         <v>2.31</v>
@@ -3189,13 +3189,13 @@
         <v>2.41</v>
       </c>
       <c r="X14" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA14" t="n">
         <v>1.01</v>
@@ -3210,10 +3210,10 @@
         <v>2.59</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
         <v>3.5</v>
@@ -3228,10 +3228,10 @@
         <v>1.01</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AM14" t="n">
         <v>1.22</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BC14" t="n">
         <v>2.44</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="BE14" t="n">
         <v>1.46</v>
@@ -3365,10 +3365,10 @@
         <v>2.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R15" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
@@ -3392,7 +3392,7 @@
         <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AA15" t="n">
         <v>1.01</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW12" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AX12" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AY12" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.58</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>7.5</v>
+        <v>4.52</v>
       </c>
       <c r="S13" t="n">
-        <v>1.73</v>
+        <v>2.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>2.09</v>
       </c>
       <c r="U13" t="n">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG13" t="n">
         <v>3.5</v>
       </c>
-      <c r="X13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AY13" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>3.58</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -840,22 +840,22 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1037,22 +1037,22 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,137 +2373,137 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>7.5</v>
+        <v>4.52</v>
       </c>
       <c r="S12" t="n">
-        <v>1.73</v>
+        <v>2.42</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.09</v>
       </c>
       <c r="U12" t="n">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG12" t="n">
         <v>3.5</v>
       </c>
-      <c r="X12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AY12" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>3.58</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW13" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AX13" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AY13" t="n">
         <v>1.25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.58</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3559,19 +3559,19 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>4.53</v>
+        <v>4.1</v>
       </c>
       <c r="S16" t="n">
         <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U16" t="n">
         <v>4.75</v>
@@ -3595,13 +3595,13 @@
         <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
         <v>1.37</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AE16" t="n">
         <v>2.12</v>
@@ -3610,22 +3610,22 @@
         <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" t="n">
         <v>8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AM16" t="n">
         <v>1.3</v>
@@ -3637,55 +3637,55 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.16</v>
+        <v>2.63</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.32</v>
+        <v>3.65</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="BB16" t="n">
         <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BD16" t="n">
         <v>3.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4425,40 +4425,40 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.48</v>
+        <v>3.16</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.62</v>
+        <v>2.77</v>
       </c>
       <c r="BB20" t="n">
         <v>1.24</v>
@@ -4544,16 +4544,16 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
         <v>4.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="T21" t="n">
         <v>2.2</v>
@@ -4562,16 +4562,16 @@
         <v>4.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="X21" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
         <v>7.2</v>
@@ -4580,34 +4580,34 @@
         <v>1.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
         <v>3.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL21" t="n">
         <v>1.95</v>
@@ -4625,10 +4625,10 @@
         <v>1.28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="AS21" t="n">
         <v>2.5</v>
@@ -4664,13 +4664,13 @@
         <v>2.1</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>11.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>11.24</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="n">
         <v>3.1</v>
@@ -5150,7 +5150,7 @@
         <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="V24" t="n">
         <v>1.4</v>
@@ -5159,13 +5159,13 @@
         <v>2.48</v>
       </c>
       <c r="X24" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="Y24" t="n">
         <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA24" t="n">
         <v>1.01</v>
@@ -5177,7 +5177,7 @@
         <v>1.37</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AE24" t="n">
         <v>2.15</v>
@@ -5204,49 +5204,49 @@
         <v>1.83</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="AT24" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="BB24" t="n">
         <v>1.25</v>
@@ -5550,7 +5550,7 @@
         <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="X26" t="n">
         <v>2.88</v>
@@ -5568,16 +5568,16 @@
         <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
         <v>4</v>
@@ -5586,73 +5586,73 @@
         <v>1.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.02</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.57</v>
+        <v>3.67</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="BA26" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BB26" t="n">
         <v>1.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF26" t="n">
         <v>1.13</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1201,7 +1201,7 @@
         <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="S4" t="n">
         <v>2.4</v>
@@ -1213,16 +1213,16 @@
         <v>4.45</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>3.09</v>
+        <v>2.81</v>
       </c>
       <c r="X4" t="n">
         <v>2.73</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
         <v>6.55</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
         <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>4.52</v>
+        <v>4.46</v>
       </c>
       <c r="S12" t="n">
         <v>2.42</v>
@@ -2798,13 +2798,13 @@
         <v>3.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.3</v>
+        <v>6.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
         <v>1.06</v>
@@ -2831,7 +2831,7 @@
         <v>7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK12" t="n">
         <v>1.85</v>
@@ -2849,52 +2849,52 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX12" t="n">
         <v>1.38</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AY12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.51</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BB12" t="n">
         <v>1.29</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="BD12" t="n">
         <v>3.58</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF12" t="n">
         <v>1.13</v>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Q13" t="n">
         <v>5</v>
@@ -2989,7 +2989,7 @@
         <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="X13" t="n">
         <v>2.32</v>
@@ -3001,7 +3001,7 @@
         <v>4.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AB13" t="n">
         <v>1.02</v>
@@ -3031,7 +3031,7 @@
         <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AL13" t="n">
         <v>1.93</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.1</v>
+        <v>4.64</v>
       </c>
       <c r="S16" t="n">
         <v>2.3</v>
@@ -3574,7 +3574,7 @@
         <v>2.05</v>
       </c>
       <c r="U16" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="V16" t="n">
         <v>1.44</v>
@@ -3625,13 +3625,13 @@
         <v>1.91</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AM16" t="n">
         <v>1.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
         <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="S20" t="n">
         <v>2.4</v>
@@ -4365,13 +4365,13 @@
         <v>4.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="X20" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="Y20" t="n">
         <v>1.33</v>
@@ -4380,7 +4380,7 @@
         <v>7.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB20" t="n">
         <v>1.06</v>
@@ -4392,7 +4392,7 @@
         <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
         <v>1.67</v>
@@ -4404,7 +4404,7 @@
         <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.06</v>
@@ -4425,49 +4425,49 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.16</v>
+        <v>3.48</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.77</v>
+        <v>3.62</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BC20" t="n">
         <v>2.25</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="BE20" t="n">
         <v>1.55</v>
@@ -4544,37 +4544,37 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="Q21" t="n">
         <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>4.32</v>
+        <v>3.95</v>
       </c>
       <c r="S21" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
         <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="X21" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AA21" t="n">
         <v>1.04</v>
@@ -4583,19 +4583,19 @@
         <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.24</v>
+        <v>3.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AH21" t="n">
         <v>1.29</v>
@@ -4613,7 +4613,7 @@
         <v>1.95</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
         <v>1.91</v>
@@ -4625,7 +4625,7 @@
         <v>1.28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AR21" t="n">
         <v>1.94</v>
@@ -4649,7 +4649,7 @@
         <v>1.43</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AZ21" t="n">
         <v>1.63</v>
@@ -4661,7 +4661,7 @@
         <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BD21" t="n">
         <v>3.5</v>
@@ -4938,19 +4938,19 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="S23" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="T23" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
         <v>11.24</v>
@@ -4974,13 +4974,13 @@
         <v>1.13</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
         <v>1.17</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AE23" t="n">
         <v>1.53</v>
@@ -4995,7 +4995,7 @@
         <v>1.53</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.18</v>
@@ -5007,7 +5007,7 @@
         <v>1.67</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AN23" t="n">
         <v>4.4</v>
@@ -5016,52 +5016,52 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="AW23" t="n">
         <v>2.14</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="BB23" t="n">
         <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BD23" t="n">
         <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BF23" t="n">
         <v>1.25</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
         <v>2.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T26" t="n">
         <v>2.05</v>
@@ -5550,10 +5550,10 @@
         <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="X26" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="Y26" t="n">
         <v>1.36</v>
@@ -5568,16 +5568,16 @@
         <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
         <v>4</v>
@@ -5586,61 +5586,61 @@
         <v>1.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.02</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="BB26" t="n">
         <v>1.3</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -998,43 +998,43 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.95</v>
+        <v>4.65</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC3" t="n">
         <v>1.27</v>
@@ -1046,31 +1046,31 @@
         <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AH3" t="n">
         <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R4" t="n">
         <v>3.6</v>
@@ -1210,7 +1210,7 @@
         <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
       <c r="V4" t="n">
         <v>1.38</v>
@@ -1228,7 +1228,7 @@
         <v>6.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
@@ -1240,19 +1240,19 @@
         <v>3.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AH4" t="n">
         <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.98</v>
+        <v>6.09</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.08</v>
@@ -1264,10 +1264,10 @@
         <v>2</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>1.84</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="AT4" t="n">
         <v>3.55</v>
@@ -1294,7 +1294,7 @@
         <v>2.39</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AX4" t="n">
         <v>1.48</v>
@@ -1303,7 +1303,7 @@
         <v>1.27</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BA4" t="n">
         <v>2.63</v>
@@ -1312,13 +1312,13 @@
         <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BD4" t="n">
         <v>3.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="BF4" t="n">
         <v>1.17</v>
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>4.55</v>
       </c>
       <c r="R7" t="n">
-        <v>5.2</v>
+        <v>8.1</v>
       </c>
       <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK7" t="n">
         <v>2.1</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2380,31 +2380,31 @@
         <v>9.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.58</v>
+        <v>5.9</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="X10" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="Z10" t="n">
         <v>4.9</v>
@@ -2428,7 +2428,7 @@
         <v>2.46</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="n">
         <v>1.57</v>
@@ -2437,7 +2437,7 @@
         <v>3.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
         <v>1.95</v>
@@ -2446,58 +2446,58 @@
         <v>1.75</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AR10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX10" t="n">
         <v>1.66</v>
       </c>
-      <c r="AS10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AY10" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
         <v>1.91</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2780,7 +2780,7 @@
         <v>4.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
         <v>2.09</v>
@@ -2795,37 +2795,37 @@
         <v>2.69</v>
       </c>
       <c r="X12" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="Y12" t="n">
         <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.25</v>
+        <v>7.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB12" t="n">
         <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
         <v>3.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" t="n">
         <v>7</v>
@@ -2849,22 +2849,22 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.68</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="AV12" t="n">
         <v>2.02</v>
@@ -2873,10 +2873,10 @@
         <v>1.62</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.51</v>
@@ -2888,13 +2888,13 @@
         <v>1.29</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
         <v>1.13</v>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>5.22</v>
       </c>
       <c r="R13" t="n">
         <v>7.5</v>
@@ -2995,19 +2995,19 @@
         <v>2.32</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AD13" t="n">
         <v>4.3</v>
@@ -3025,7 +3025,7 @@
         <v>1.53</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AJ13" t="n">
         <v>1.2</v>
@@ -3034,7 +3034,7 @@
         <v>1.87</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AM13" t="n">
         <v>1.17</v>
@@ -3049,10 +3049,10 @@
         <v>1.26</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AS13" t="n">
         <v>2.44</v>
@@ -3064,7 +3064,7 @@
         <v>3.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="AW13" t="n">
         <v>1.8</v>
@@ -3076,13 +3076,13 @@
         <v>1.25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BA13" t="n">
         <v>4.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BC13" t="n">
         <v>1.85</v>
@@ -3183,10 +3183,10 @@
         <v>2.31</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="X14" t="n">
         <v>3.1</v>
@@ -3195,7 +3195,7 @@
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>1.01</v>
@@ -3210,13 +3210,13 @@
         <v>2.59</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AF14" t="n">
         <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AH14" t="n">
         <v>1.19</v>
@@ -3231,10 +3231,10 @@
         <v>2.15</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AN14" t="n">
         <v>1.1</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BC14" t="n">
         <v>2.44</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="BE14" t="n">
         <v>1.46</v>
@@ -3368,7 +3368,7 @@
         <v>3.15</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
@@ -3383,7 +3383,7 @@
         <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="X15" t="n">
         <v>3.28</v>
@@ -3404,16 +3404,16 @@
         <v>1.43</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AF15" t="n">
         <v>1.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AH15" t="n">
         <v>1.17</v>
@@ -3443,7 +3443,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AR15" t="n">
         <v>2.28</v>
@@ -3455,10 +3455,10 @@
         <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AW15" t="n">
         <v>1.53</v>
@@ -3467,13 +3467,13 @@
         <v>1.32</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AZ15" t="n">
         <v>1.93</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BB15" t="n">
         <v>1.33</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,137 +2373,137 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>5.22</v>
       </c>
       <c r="R12" t="n">
-        <v>4.46</v>
+        <v>7.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.09</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>4.95</v>
+        <v>6.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="X12" t="n">
-        <v>3.03</v>
+        <v>2.32</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC12" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="AH12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY12" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AZ12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC12" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="BD12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
         <v>1.31</v>
       </c>
-      <c r="Q13" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="AQ13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS13" t="n">
         <v>2.63</v>
       </c>
-      <c r="U13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AT13" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AZ13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.29</v>
       </c>
-      <c r="BA13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BC13" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>11.24</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>11.24</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="R7" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="T7" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="V7" t="n">
         <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="X7" t="n">
         <v>2.5</v>
@@ -1816,13 +1816,13 @@
         <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="AA7" t="n">
         <v>1.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
         <v>1.18</v>
@@ -1837,28 +1837,28 @@
         <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH7" t="n">
         <v>1.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
         <v>1.31</v>
       </c>
-      <c r="Q12" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="AQ12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS12" t="n">
         <v>2.63</v>
       </c>
-      <c r="U12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AT12" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AZ12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB12" t="n">
         <v>1.29</v>
       </c>
-      <c r="BA12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BC12" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>5.22</v>
       </c>
       <c r="R13" t="n">
-        <v>4.46</v>
+        <v>7.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="T13" t="n">
-        <v>2.09</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>4.95</v>
+        <v>6.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="X13" t="n">
-        <v>3.03</v>
+        <v>2.32</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC13" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK13" t="n">
+      <c r="AZ13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="BD13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>11.24</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>11.24</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>6.5</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AA3" t="n">
         <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.04</v>
+        <v>2.59</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="S4" t="n">
         <v>2.4</v>
@@ -1237,22 +1237,22 @@
         <v>1.24</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.09</v>
+        <v>5.4</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.08</v>
@@ -1276,13 +1276,13 @@
         <v>1.38</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AT4" t="n">
         <v>3.55</v>
@@ -1291,19 +1291,19 @@
         <v>2.75</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AY4" t="n">
         <v>1.27</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="BA4" t="n">
         <v>2.63</v>
@@ -1312,13 +1312,13 @@
         <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BD4" t="n">
         <v>3.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="BF4" t="n">
         <v>1.17</v>
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4.21</v>
+        <v>3.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>2.27</v>
+        <v>1.88</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
         <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>4.46</v>
+        <v>4.63</v>
       </c>
       <c r="S12" t="n">
         <v>2.3</v>
@@ -2795,7 +2795,7 @@
         <v>2.69</v>
       </c>
       <c r="X12" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="Y12" t="n">
         <v>1.4</v>
@@ -2822,7 +2822,7 @@
         <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AH12" t="n">
         <v>1.25</v>
@@ -2834,13 +2834,13 @@
         <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL12" t="n">
         <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
         <v>1.95</v>
@@ -2849,22 +2849,22 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.68</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.58</v>
+        <v>3.37</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="AV12" t="n">
         <v>2.02</v>
@@ -2873,10 +2873,10 @@
         <v>1.62</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.51</v>
@@ -2885,7 +2885,7 @@
         <v>3.05</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BC12" t="n">
         <v>2.25</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.22</v>
+        <v>5.15</v>
       </c>
       <c r="R13" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="S13" t="n">
         <v>1.73</v>
@@ -2995,7 +2995,7 @@
         <v>2.32</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Z13" t="n">
         <v>5</v>
@@ -3010,22 +3010,22 @@
         <v>1.17</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AJ13" t="n">
         <v>1.2</v>
@@ -3040,43 +3040,43 @@
         <v>1.17</v>
       </c>
       <c r="AN13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="AT13" t="n">
         <v>2.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BA13" t="n">
         <v>4.4</v>
@@ -3085,16 +3085,16 @@
         <v>1.14</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q16" t="n">
         <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.64</v>
+        <v>4.39</v>
       </c>
       <c r="S16" t="n">
         <v>2.3</v>
@@ -3580,10 +3580,10 @@
         <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="X16" t="n">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
@@ -3598,16 +3598,16 @@
         <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD16" t="n">
         <v>2.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
         <v>3.9</v>
@@ -3625,10 +3625,10 @@
         <v>1.91</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AN16" t="n">
         <v>1.96</v>
@@ -3643,16 +3643,16 @@
         <v>1.54</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AS16" t="n">
         <v>2.44</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.63</v>
+        <v>3.32</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.65</v>
+        <v>3.17</v>
       </c>
       <c r="AV16" t="n">
         <v>2.29</v>
@@ -3664,16 +3664,16 @@
         <v>1.47</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AZ16" t="n">
         <v>1.44</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC16" t="n">
         <v>2.3</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4347,19 +4347,19 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q20" t="n">
         <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="S20" t="n">
         <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
         <v>4.2</v>
@@ -4371,7 +4371,7 @@
         <v>2.81</v>
       </c>
       <c r="X20" t="n">
-        <v>3.06</v>
+        <v>2.91</v>
       </c>
       <c r="Y20" t="n">
         <v>1.33</v>
@@ -4398,13 +4398,13 @@
         <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="AH20" t="n">
         <v>1.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.45</v>
+        <v>5.8</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.06</v>
@@ -4455,25 +4455,25 @@
         <v>1.22</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.62</v>
+        <v>2.7</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="S21" t="n">
         <v>2.3</v>
@@ -4568,10 +4568,10 @@
         <v>2.85</v>
       </c>
       <c r="X21" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Z21" t="n">
         <v>7.1</v>
@@ -4583,16 +4583,16 @@
         <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="AE21" t="n">
         <v>1.96</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG21" t="n">
         <v>3.18</v>
@@ -4601,7 +4601,7 @@
         <v>1.29</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.1</v>
@@ -4622,40 +4622,40 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AR21" t="n">
         <v>1.94</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AT21" t="n">
         <v>3.42</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="BB21" t="n">
         <v>1.25</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4938,115 +4938,115 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="R23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S23" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T23" t="n">
         <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>11.24</v>
+        <v>11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AD23" t="n">
         <v>4.8</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="n">
         <v>1.53</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AS23" t="n">
         <v>1.86</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="BA23" t="n">
         <v>12</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,46 +5529,46 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S26" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="U26" t="n">
         <v>2.75</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W26" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="X26" t="n">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AD26" t="n">
         <v>2.8</v>
@@ -5589,13 +5589,13 @@
         <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AK26" t="n">
         <v>1.85</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AM26" t="n">
         <v>1.33</v>
@@ -5607,37 +5607,37 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AR26" t="n">
         <v>1.89</v>
       </c>
       <c r="AS26" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AW26" t="n">
         <v>2.05</v>
       </c>
-      <c r="AT26" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AX26" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="BA26" t="n">
         <v>2.02</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -819,7 +819,7 @@
         <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
         <v>2.75</v>
@@ -846,10 +846,10 @@
         <v>3.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
         <v>3.5</v>
@@ -879,34 +879,34 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="S4" t="n">
         <v>2.4</v>
@@ -1210,7 +1210,7 @@
         <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="V4" t="n">
         <v>1.38</v>
@@ -1225,7 +1225,7 @@
         <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="AA4" t="n">
         <v>1.05</v>
@@ -1246,13 +1246,13 @@
         <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AH4" t="n">
         <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.4</v>
+        <v>6.14</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.08</v>
@@ -1267,7 +1267,7 @@
         <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,13 +1276,13 @@
         <v>1.38</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AT4" t="n">
         <v>3.55</v>
@@ -1291,13 +1291,13 @@
         <v>2.75</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AY4" t="n">
         <v>1.27</v>
@@ -1309,7 +1309,7 @@
         <v>2.63</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC4" t="n">
         <v>2.1</v>
@@ -1789,10 +1789,10 @@
         <v>1.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>1.95</v>
@@ -1822,7 +1822,7 @@
         <v>1.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
         <v>1.18</v>
@@ -1837,61 +1837,61 @@
         <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH7" t="n">
         <v>1.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>4.63</v>
+        <v>7.91</v>
       </c>
       <c r="S12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.3</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AG12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
         <v>3.1</v>
       </c>
-      <c r="AE12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AR12" t="n">
         <v>2.12</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.57</v>
+        <v>2.37</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.37</v>
+        <v>2.7</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.4</v>
+        <v>4.65</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q13" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.28</v>
-      </c>
       <c r="W13" t="n">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="X13" t="n">
-        <v>2.32</v>
+        <v>2.94</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AR13" t="n">
         <v>2.12</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.37</v>
+        <v>2.57</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.7</v>
+        <v>3.37</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.65</v>
+        <v>3.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.8</v>
+        <v>4.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S14" t="n">
         <v>4.76</v>
@@ -3183,10 +3183,10 @@
         <v>2.31</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="X14" t="n">
         <v>3.1</v>
@@ -3210,10 +3210,10 @@
         <v>2.59</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
         <v>4.33</v>
@@ -3234,43 +3234,43 @@
         <v>1.61</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BC14" t="n">
         <v>2.44</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="BE14" t="n">
         <v>1.46</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>4.65</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.53</v>
       </c>
-      <c r="AF22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.53</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U23" t="n">
-        <v>11</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>7.5</v>
+        <v>1.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AA2" t="n">
         <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AF2" t="n">
         <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.04</v>
+        <v>2.59</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF2" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.45</v>
+        <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R3" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="AA3" t="n">
         <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.59</v>
+        <v>1.04</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,28 +1195,28 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R4" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="T4" t="n">
         <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
         <v>2.73</v>
@@ -1225,37 +1225,37 @@
         <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.14</v>
+        <v>5.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
         <v>1.73</v>
@@ -1264,52 +1264,52 @@
         <v>2</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.55</v>
+        <v>3.07</v>
       </c>
       <c r="AU4" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BA4" t="n">
         <v>2.75</v>
       </c>
-      <c r="AV4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.63</v>
-      </c>
       <c r="BB4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
         <v>2.1</v>
@@ -1321,7 +1321,7 @@
         <v>1.67</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,137 +1979,137 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,52 +2771,52 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q12" t="n">
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>7.91</v>
+        <v>7.8</v>
       </c>
       <c r="S12" t="n">
         <v>1.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="X12" t="n">
         <v>2.32</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AB12" t="n">
         <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
         <v>2.3</v>
@@ -2825,19 +2825,19 @@
         <v>2.45</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI12" t="n">
         <v>4.2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AM12" t="n">
         <v>1.17</v>
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.53</v>
@@ -2861,7 +2861,7 @@
         <v>2.37</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="AU12" t="n">
         <v>3.15</v>
@@ -2870,10 +2870,10 @@
         <v>2.35</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AY12" t="n">
         <v>1.31</v>
@@ -2882,19 +2882,19 @@
         <v>1.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
         <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="BF12" t="n">
         <v>1.25</v>
@@ -2968,37 +2968,37 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="R13" t="n">
-        <v>4.63</v>
+        <v>4.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W13" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="X13" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA13" t="n">
         <v>1.03</v>
@@ -3007,94 +3007,94 @@
         <v>1.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI13" t="n">
-        <v>7</v>
+        <v>5.64</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL13" t="n">
         <v>1.85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="AS13" t="n">
         <v>2.57</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.37</v>
+        <v>3.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="BE13" t="n">
         <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,19 +3165,19 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.98</v>
+        <v>4.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>4.76</v>
+        <v>5.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>2.31</v>
@@ -3228,16 +3228,16 @@
         <v>1.01</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>1.28</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="BD14" t="n">
         <v>3.15</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BF14" t="n">
         <v>1.08</v>
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="U15" t="n">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="V15" t="n">
         <v>1.5</v>
@@ -3386,13 +3386,13 @@
         <v>2.39</v>
       </c>
       <c r="X15" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.01</v>
@@ -3401,79 +3401,79 @@
         <v>1.05</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN15" t="n">
         <v>1.43</v>
       </c>
-      <c r="AD15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX15" t="n">
         <v>1.53</v>
       </c>
-      <c r="AG15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX15" t="n">
+      <c r="AY15" t="n">
         <v>1.32</v>
       </c>
-      <c r="AY15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="BB15" t="n">
         <v>1.33</v>
@@ -3482,13 +3482,13 @@
         <v>2.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,34 +3559,34 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>4.39</v>
+        <v>4.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="T16" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="U16" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="X16" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
         <v>8</v>
@@ -3595,85 +3595,85 @@
         <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AI16" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN16" t="n">
         <v>1.91</v>
       </c>
-      <c r="AL16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.32</v>
+        <v>2.63</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.17</v>
+        <v>3.65</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC16" t="n">
         <v>2.3</v>
@@ -3682,7 +3682,7 @@
         <v>3.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BF16" t="n">
         <v>1.13</v>
@@ -3759,10 +3759,10 @@
         <v>1.47</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="S17" t="n">
         <v>1.9</v>
@@ -3795,28 +3795,28 @@
         <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AD17" t="n">
         <v>5.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
         <v>1.53</v>
@@ -3962,7 +3962,7 @@
         <v>4.8</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T18" t="n">
         <v>2.02</v>
@@ -3971,10 +3971,10 @@
         <v>5.58</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="X18" t="n">
         <v>2.97</v>
@@ -3992,22 +3992,22 @@
         <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AD18" t="n">
         <v>3.04</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" t="n">
         <v>7.3</v>
@@ -4016,7 +4016,7 @@
         <v>1.03</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL18" t="n">
         <v>1.77</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
         <v>2.4</v>
@@ -4347,31 +4347,31 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
         <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="X20" t="n">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="Y20" t="n">
         <v>1.33</v>
@@ -4380,43 +4380,43 @@
         <v>7.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
         <v>1.83</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
         <v>1.75</v>
@@ -4425,46 +4425,46 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.48</v>
+        <v>3.16</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AZ20" t="n">
         <v>1.57</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.7</v>
+        <v>3.33</v>
       </c>
       <c r="BB20" t="n">
         <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BD20" t="n">
         <v>3.25</v>
@@ -5144,22 +5144,22 @@
         <v>2.04</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3</v>
+        <v>3.78</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="U24" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
         <v>2.48</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
         <v>1.28</v>
@@ -5171,43 +5171,43 @@
         <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5243,7 +5243,7 @@
         <v>1.19</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="BA24" t="n">
         <v>1.6</v>
@@ -5252,7 +5252,7 @@
         <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="BD24" t="n">
         <v>3.1</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.45</v>
+        <v>7.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R2" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U2" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="X2" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
         <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.59</v>
+        <v>1.04</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>7.5</v>
+        <v>1.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AA3" t="n">
         <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AF3" t="n">
         <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.04</v>
+        <v>2.59</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3559,16 +3559,16 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>4.53</v>
+        <v>4.48</v>
       </c>
       <c r="S16" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
         <v>2.04</v>
@@ -3613,7 +3613,7 @@
         <v>3.74</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" t="n">
         <v>7.4</v>
@@ -3670,7 +3670,7 @@
         <v>1.57</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BB16" t="n">
         <v>1.25</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="R17" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.51</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>5.37</v>
+        <v>5.58</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="X17" t="n">
-        <v>2.06</v>
+        <v>2.97</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
         <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.25</v>
+        <v>3.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.38</v>
+        <v>2.01</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AM17" t="n">
+      <c r="BC17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.02</v>
+        <v>2.51</v>
       </c>
       <c r="U18" t="n">
-        <v>5.58</v>
+        <v>5.37</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="X18" t="n">
-        <v>2.97</v>
+        <v>2.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AB18" t="n">
         <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.04</v>
+        <v>5.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.01</v>
+        <v>1.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.3</v>
+        <v>3.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.77</v>
+        <v>2.29</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.22</v>
+        <v>1.63</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4350,10 +4350,10 @@
         <v>1.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>3.81</v>
+        <v>3.85</v>
       </c>
       <c r="S20" t="n">
         <v>2.33</v>
@@ -4365,13 +4365,13 @@
         <v>4.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="X20" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="Y20" t="n">
         <v>1.33</v>
@@ -4386,7 +4386,7 @@
         <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AD20" t="n">
         <v>2.92</v>
@@ -4410,7 +4410,7 @@
         <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
         <v>1.92</v>
@@ -4428,37 +4428,37 @@
         <v>1.24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.32</v>
+        <v>3.49</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AZ20" t="n">
         <v>1.57</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BB20" t="n">
         <v>1.29</v>
@@ -4547,16 +4547,16 @@
         <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
         <v>4.5</v>
@@ -4568,19 +4568,19 @@
         <v>2.85</v>
       </c>
       <c r="X21" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="Y21" t="n">
         <v>1.39</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.1</v>
+        <v>6.25</v>
       </c>
       <c r="AA21" t="n">
         <v>1.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC21" t="n">
         <v>1.27</v>
@@ -4589,31 +4589,31 @@
         <v>3.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
         <v>3.18</v>
       </c>
       <c r="AH21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM21" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
         <v>1.91</v>
@@ -4625,7 +4625,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AR21" t="n">
         <v>1.94</v>
@@ -4634,13 +4634,13 @@
         <v>2.45</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AU21" t="n">
         <v>3.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AW21" t="n">
         <v>1.8</v>
@@ -4649,28 +4649,28 @@
         <v>1.49</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BA21" t="n">
         <v>3</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.53</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U22" t="n">
-        <v>11</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>15.85</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>11.69</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE23" t="n">
         <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
         <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="S24" t="n">
         <v>3.78</v>
@@ -5171,7 +5171,7 @@
         <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
         <v>1.4</v>
@@ -5180,10 +5180,10 @@
         <v>2.83</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG24" t="n">
         <v>3.88</v>
@@ -5213,31 +5213,31 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AY24" t="n">
         <v>1.19</v>
@@ -5246,7 +5246,7 @@
         <v>2.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="BB24" t="n">
         <v>1.3</v>
@@ -5529,43 +5529,43 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="R26" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="S26" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="T26" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="U26" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V26" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="X26" t="n">
         <v>2.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AA26" t="n">
         <v>1.01</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC26" t="n">
         <v>1.34</v>
@@ -5583,7 +5583,7 @@
         <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AI26" t="n">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.85</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AM26" t="n">
         <v>1.33</v>
@@ -5607,16 +5607,16 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AT26" t="n">
         <v>2.68</v>
@@ -5625,19 +5625,19 @@
         <v>3.67</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AY26" t="n">
         <v>1.41</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="BA26" t="n">
         <v>2.02</v>
@@ -5652,10 +5652,10 @@
         <v>3.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>7.5</v>
+        <v>1.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AA2" t="n">
         <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AF2" t="n">
         <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.04</v>
+        <v>2.59</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF2" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.45</v>
+        <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R3" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="AA3" t="n">
         <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.59</v>
+        <v>1.04</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,137 +1979,137 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>15.85</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>11.69</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE22" t="n">
         <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>15.85</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>11.69</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>1.53</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="R2" t="n">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -828,10 +828,10 @@
         <v>3.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="AA2" t="n">
         <v>1.04</v>
@@ -849,7 +849,7 @@
         <v>2.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG2" t="n">
         <v>3.76</v>
@@ -864,10 +864,10 @@
         <v>1.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AM2" t="n">
         <v>1.21</v>
@@ -918,13 +918,13 @@
         <v>1.27</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BD2" t="n">
         <v>3.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="BF2" t="n">
         <v>1.12</v>
@@ -1392,28 +1392,28 @@
         </is>
       </c>
       <c r="P5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U5" t="n">
         <v>3</v>
       </c>
-      <c r="Q5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.26</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X5" t="n">
         <v>3.5</v>
@@ -1431,19 +1431,19 @@
         <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AH5" t="n">
         <v>1.12</v>
@@ -1458,13 +1458,13 @@
         <v>2.01</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
         <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="S6" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
         <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
         <v>1.45</v>
@@ -1613,7 +1613,7 @@
         <v>2.47</v>
       </c>
       <c r="X6" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="Y6" t="n">
         <v>1.37</v>
@@ -1634,13 +1634,13 @@
         <v>3.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AH6" t="n">
         <v>1.3</v>
@@ -1667,43 +1667,43 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="BC6" t="n">
         <v>2.1</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,137 +2373,137 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3562,13 +3562,13 @@
         <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R16" t="n">
-        <v>4.48</v>
+        <v>4.1</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
         <v>2.04</v>
@@ -3583,25 +3583,25 @@
         <v>2.65</v>
       </c>
       <c r="X16" t="n">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="Y16" t="n">
         <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AA16" t="n">
         <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="AE16" t="n">
         <v>2.15</v>
@@ -3610,13 +3610,13 @@
         <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AH16" t="n">
         <v>1.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.06</v>
@@ -3628,10 +3628,10 @@
         <v>1.68</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>1.68</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="AT16" t="n">
         <v>2.63</v>
@@ -3658,10 +3658,10 @@
         <v>2.65</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AY16" t="n">
         <v>1.42</v>
@@ -3673,7 +3673,7 @@
         <v>3.23</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC16" t="n">
         <v>2.3</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R17" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="S17" t="n">
         <v>2.25</v>
@@ -3956,10 +3956,10 @@
         <v>1.47</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="R18" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="S18" t="n">
         <v>1.9</v>
@@ -3971,10 +3971,10 @@
         <v>5.37</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="X18" t="n">
         <v>2.06</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
         <v>2.4</v>
@@ -4201,7 +4201,7 @@
         <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AH19" t="n">
         <v>1.32</v>
@@ -4353,70 +4353,70 @@
         <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="S20" t="n">
         <v>2.33</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
         <v>4.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="X20" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="Y20" t="n">
         <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
         <v>1.04</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AN20" t="n">
         <v>1.75</v>
@@ -4428,52 +4428,52 @@
         <v>1.24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="AT20" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.49</v>
+        <v>3.33</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.23</v>
+        <v>2.44</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC20" t="n">
         <v>2.25</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,76 +4544,76 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="S21" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="T21" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
         <v>4.5</v>
       </c>
       <c r="V21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.37</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.39</v>
       </c>
       <c r="Z21" t="n">
         <v>6.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC21" t="n">
         <v>1.27</v>
       </c>
       <c r="AD21" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG21" t="n">
         <v>3.3</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.18</v>
       </c>
       <c r="AH21" t="n">
         <v>1.3</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AL21" t="n">
         <v>1.89</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN21" t="n">
         <v>1.91</v>
@@ -4622,55 +4622,55 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AT21" t="n">
         <v>3.35</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="AW21" t="n">
         <v>1.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="BA21" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4747,31 +4747,31 @@
         <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>15.85</v>
+        <v>17.18</v>
       </c>
       <c r="S22" t="n">
         <v>1.49</v>
       </c>
       <c r="T22" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U22" t="n">
-        <v>11.69</v>
+        <v>12.46</v>
       </c>
       <c r="V22" t="n">
         <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="X22" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AA22" t="n">
         <v>1.14</v>
@@ -4783,7 +4783,7 @@
         <v>1.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>1.53</v>
@@ -4795,10 +4795,10 @@
         <v>2.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.22</v>
@@ -4813,40 +4813,40 @@
         <v>1</v>
       </c>
       <c r="AN22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AU22" t="n">
         <v>3.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AW22" t="n">
         <v>2.16</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AZ22" t="n">
         <v>1.16</v>
@@ -4858,13 +4858,13 @@
         <v>1.13</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="BD22" t="n">
         <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BF22" t="n">
         <v>1.25</v>
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.37</v>
+        <v>2.14</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5532,10 +5532,10 @@
         <v>3.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R26" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S26" t="n">
         <v>3.76</v>
@@ -5550,13 +5550,13 @@
         <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="X26" t="n">
         <v>2.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
         <v>7</v>
@@ -5565,7 +5565,7 @@
         <v>1.01</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
         <v>1.34</v>
@@ -5586,13 +5586,13 @@
         <v>1.21</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL26" t="n">
         <v>1.85</v>
@@ -5607,40 +5607,40 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.67</v>
+        <v>3.89</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AW26" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AZ26" t="n">
         <v>2.15</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="BB26" t="n">
         <v>1.3</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="R2" t="n">
-        <v>7.75</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T2" t="n">
         <v>2.05</v>
@@ -849,7 +849,7 @@
         <v>2.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG2" t="n">
         <v>3.76</v>
@@ -867,10 +867,10 @@
         <v>2.29</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AN2" t="n">
         <v>2.59</v>
@@ -998,67 +998,67 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>7.5</v>
+        <v>8.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
         <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="X3" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.04</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
         <v>2.38</v>
@@ -1067,16 +1067,16 @@
         <v>1.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AQ3" t="n">
         <v>2.21</v>
@@ -1115,16 +1115,16 @@
         <v>1.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="BD3" t="n">
         <v>3.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,16 +1195,16 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="R4" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="S4" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="T4" t="n">
         <v>2.2</v>
@@ -1219,7 +1219,7 @@
         <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="Y4" t="n">
         <v>1.4</v>
@@ -1231,73 +1231,73 @@
         <v>1.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AH4" t="n">
         <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.7</v>
+        <v>5.15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AM4" t="n">
         <v>1.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.07</v>
+        <v>2.87</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.19</v>
+        <v>3.42</v>
       </c>
       <c r="AV4" t="n">
         <v>2.07</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AY4" t="n">
         <v>1.24</v>
@@ -1309,19 +1309,19 @@
         <v>2.75</v>
       </c>
       <c r="BB4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF4" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>3.44</v>
+        <v>4.29</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="V5" t="n">
         <v>1.56</v>
@@ -1416,55 +1416,55 @@
         <v>2.24</v>
       </c>
       <c r="X5" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="Y5" t="n">
         <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK5" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1509,13 +1509,13 @@
         <v>1.31</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BD5" t="n">
         <v>2.97</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BF5" t="n">
         <v>1.08</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S6" t="n">
         <v>4.2</v>
@@ -1634,7 +1634,7 @@
         <v>3.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
         <v>1.85</v>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="R7" t="n">
-        <v>8.039999999999999</v>
+        <v>8</v>
       </c>
       <c r="S7" t="n">
         <v>1.95</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
         <v>6.5</v>
@@ -1807,7 +1807,7 @@
         <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="X7" t="n">
         <v>2.5</v>
@@ -1816,7 +1816,7 @@
         <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="AA7" t="n">
         <v>1.06</v>
@@ -1825,13 +1825,13 @@
         <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
         <v>2.05</v>
@@ -1840,10 +1840,10 @@
         <v>2.7</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.15</v>
@@ -1855,10 +1855,10 @@
         <v>1.67</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,7 +1867,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AR7" t="n">
         <v>3.21</v>
@@ -1903,7 +1903,7 @@
         <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BD7" t="n">
         <v>3.9</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2373,137 +2373,137 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>8.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.38</v>
       </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U12" t="n">
-        <v>7</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.25</v>
-      </c>
       <c r="W12" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="X12" t="n">
-        <v>2.32</v>
+        <v>2.94</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="BF12" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>1.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>5.4</v>
       </c>
       <c r="R13" t="n">
-        <v>4.45</v>
+        <v>9.34</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="T13" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>4.9</v>
+        <v>7.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="X13" t="n">
-        <v>3.03</v>
+        <v>2.34</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY13" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="S14" t="n">
         <v>5.5</v>
@@ -3213,7 +3213,7 @@
         <v>2.35</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
         <v>4.33</v>
@@ -3243,49 +3243,49 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AV14" t="n">
         <v>1.72</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AW14" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BC14" t="n">
         <v>2.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="BE14" t="n">
         <v>1.5</v>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
         <v>3</v>
@@ -3371,19 +3371,19 @@
         <v>2.5</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
         <v>1.96</v>
       </c>
       <c r="U15" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W15" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="X15" t="n">
         <v>3.2</v>
@@ -3392,49 +3392,49 @@
         <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB15" t="n">
         <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AI15" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK15" t="n">
         <v>2</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>1.28</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AR15" t="n">
         <v>1.81</v>
@@ -3458,7 +3458,7 @@
         <v>3.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AW15" t="n">
         <v>1.85</v>
@@ -3470,10 +3470,10 @@
         <v>1.32</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="BB15" t="n">
         <v>1.33</v>
@@ -3482,13 +3482,13 @@
         <v>2.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BE15" t="n">
         <v>1.45</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,16 +3559,16 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T16" t="n">
         <v>2.04</v>
@@ -3589,34 +3589,34 @@
         <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB16" t="n">
         <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
         <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="AH16" t="n">
         <v>1.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.06</v>
@@ -3676,16 +3676,16 @@
         <v>1.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3703,27 +3703,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,134 +3756,134 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI17" t="n">
         <v>4.5</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AJ17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH17" t="n">
+      <c r="AN17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI17" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46100.72916666666</v>
+        <v>46100.70833333334</v>
       </c>
     </row>
     <row r="18">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.47</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9</v>
+        <v>3.22</v>
       </c>
       <c r="T18" t="n">
-        <v>2.51</v>
+        <v>2.07</v>
       </c>
       <c r="U18" t="n">
-        <v>5.37</v>
+        <v>3.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="X18" t="n">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
         <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.25</v>
+        <v>3.45</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.63</v>
+        <v>1.31</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="AJ18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AN18" t="n">
-        <v>2.46</v>
+        <v>1.39</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.63</v>
+        <v>1.99</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.11</v>
+        <v>1.71</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.4</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.28</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="U19" t="n">
-        <v>2.96</v>
+        <v>5.36</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="X19" t="n">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
         <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.9</v>
       </c>
-      <c r="AG19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AL19" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AM19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC19" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4294,27 +4294,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="Q20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R20" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI20" t="n">
         <v>3.25</v>
       </c>
-      <c r="R20" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>6.35</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46100.77083333334</v>
+        <v>46100.72916666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="S21" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="T21" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="U21" t="n">
         <v>4.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="X21" t="n">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.25</v>
+        <v>7.1</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.6</v>
+        <v>6.45</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.05</v>
       </c>
       <c r="AK21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR21" t="n">
         <v>1.81</v>
       </c>
-      <c r="AL21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AS21" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.9</v>
+        <v>3.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46100.79166666666</v>
+        <v>46100.77083333334</v>
       </c>
     </row>
     <row r="22">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,134 +4741,134 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.15</v>
       </c>
-      <c r="Q22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>17.18</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U22" t="n">
-        <v>12.46</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46100.83333333334</v>
+        <v>46100.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>1.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.45</v>
+        <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>2.66</v>
+        <v>17.18</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>1.49</v>
       </c>
       <c r="T23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U23" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.4</v>
       </c>
-      <c r="U23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.56</v>
+        <v>2.24</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.34</v>
+        <v>1.6</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,137 +1979,137 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>8.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R12" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>9.34</v>
+        <v>4.45</v>
       </c>
       <c r="S13" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="U13" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z13" t="n">
         <v>7.5</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="BF13" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="U19" t="n">
-        <v>5.36</v>
+        <v>5.37</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="X19" t="n">
-        <v>2.97</v>
+        <v>2.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AB19" t="n">
         <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.04</v>
+        <v>5.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.02</v>
+        <v>1.38</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="AI19" t="n">
-        <v>7.3</v>
+        <v>3.25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.22</v>
+        <v>1.63</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="U20" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
       <c r="V20" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="X20" t="n">
-        <v>2.06</v>
+        <v>2.97</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
         <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.25</v>
+        <v>3.04</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.38</v>
+        <v>2.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.55</v>
+        <v>1.69</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.15</v>
+        <v>3.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AM20" t="n">
+      <c r="BC20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5131,137 +5131,137 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5328,137 +5328,137 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,29 +753,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -787,126 +787,126 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>8.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>1.98</v>
+        <v>8.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="X2" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
         <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.59</v>
+        <v>1.05</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,16 +915,16 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
         <v>1.12</v>
@@ -950,178 +950,178 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>8.16</v>
+        <v>1.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>8.5</v>
+        <v>1.98</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC3" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="BF3" t="n">
         <v>1.12</v>
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U4" t="n">
         <v>3.7</v>
       </c>
-      <c r="R4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z4" t="n">
         <v>5.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.15</v>
+        <v>5.85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
         <v>1.78</v>
@@ -1291,7 +1291,7 @@
         <v>3.42</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.07</v>
+        <v>2.52</v>
       </c>
       <c r="AW4" t="n">
         <v>1.97</v>
@@ -1300,28 +1300,28 @@
         <v>1.59</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>4.29</v>
+        <v>3.63</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="X5" t="n">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
         <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.6</v>
+        <v>5.05</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="R7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="W7" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV7" t="n">
         <v>2.05</v>
       </c>
-      <c r="AG7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="AW7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1.9</v>
       </c>
-      <c r="AR7" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1979,137 +1979,137 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>8.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2771,73 +2771,73 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>9.34</v>
+        <v>6.75</v>
       </c>
       <c r="S12" t="n">
         <v>1.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
         <v>3.5</v>
       </c>
       <c r="X12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Y12" t="n">
         <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
         <v>1.14</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AE12" t="n">
         <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="n">
         <v>1.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AM12" t="n">
         <v>1.17</v>
@@ -2861,7 +2861,7 @@
         <v>2.24</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AU12" t="n">
         <v>3.35</v>
@@ -2870,7 +2870,7 @@
         <v>2.48</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AX12" t="n">
         <v>1.57</v>
@@ -2879,7 +2879,7 @@
         <v>1.35</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BA12" t="n">
         <v>4.4</v>
@@ -2888,16 +2888,16 @@
         <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,28 +2968,28 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="R13" t="n">
         <v>4.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
         <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="X13" t="n">
         <v>2.94</v>
@@ -3010,10 +3010,10 @@
         <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
         <v>1.82</v>
@@ -3025,10 +3025,10 @@
         <v>1.24</v>
       </c>
       <c r="AI13" t="n">
-        <v>7.3</v>
+        <v>7.38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK13" t="n">
         <v>1.85</v>
@@ -3037,10 +3037,10 @@
         <v>1.85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3052,7 +3052,7 @@
         <v>1.62</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.37</v>
+        <v>1.94</v>
       </c>
       <c r="AS13" t="n">
         <v>2.45</v>
@@ -3082,19 +3082,19 @@
         <v>3.05</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="BE13" t="n">
         <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="U19" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="X19" t="n">
-        <v>2.06</v>
+        <v>2.97</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
         <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.25</v>
+        <v>3.04</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.38</v>
+        <v>2.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.55</v>
+        <v>1.69</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.15</v>
+        <v>3.58</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AM19" t="n">
+      <c r="BC19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="U20" t="n">
-        <v>5.36</v>
+        <v>5.37</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="W20" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="X20" t="n">
-        <v>2.97</v>
+        <v>2.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AB20" t="n">
         <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.04</v>
+        <v>5.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.02</v>
+        <v>1.38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.58</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="AI20" t="n">
-        <v>7.3</v>
+        <v>3.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.22</v>
+        <v>1.63</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1178,20 +1178,20 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1363,32 +1363,32 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1575,27 +1575,27 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P6" t="n">
         <v>3.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="S6" t="n">
         <v>4.2</v>
@@ -1607,10 +1607,10 @@
         <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="X6" t="n">
         <v>2.74</v>
@@ -1619,7 +1619,7 @@
         <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="AA6" t="n">
         <v>1.05</v>
@@ -1628,7 +1628,7 @@
         <v>1.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
         <v>3.3</v>
@@ -1640,7 +1640,7 @@
         <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AH6" t="n">
         <v>1.3</v>
@@ -1652,22 +1652,22 @@
         <v>1.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.52</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>8.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="X16" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="AH16" t="n">
         <v>1.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.06</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.65</v>
+        <v>3.49</v>
       </c>
       <c r="AV16" t="n">
         <v>2.65</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AZ16" t="n">
         <v>1.57</v>
@@ -3676,16 +3676,16 @@
         <v>1.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="BD16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="S17" t="n">
         <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
         <v>3.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="X17" t="n">
-        <v>2.41</v>
+        <v>2.12</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.14</v>
       </c>
       <c r="AD17" t="n">
         <v>4.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.57</v>
+        <v>2.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BC17" t="n">
         <v>1.72</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE17" t="n">
         <v>1.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="Q18" t="n">
         <v>3.3</v>
       </c>
       <c r="R18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.4</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.22</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>3.04</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.34</v>
       </c>
-      <c r="W18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.99</v>
+        <v>2.31</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>4.59</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="T19" t="n">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>5.36</v>
+        <v>4.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="X19" t="n">
-        <v>2.97</v>
+        <v>2.15</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.04</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.69</v>
+        <v>2.45</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.58</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" t="n">
-        <v>7.3</v>
+        <v>3.7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.44</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>5.25</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>5.37</v>
+        <v>2.8</v>
       </c>
       <c r="V20" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="W20" t="n">
-        <v>4.2</v>
+        <v>2.79</v>
       </c>
       <c r="X20" t="n">
-        <v>2.06</v>
+        <v>2.48</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="AH20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE20" t="n">
         <v>1.63</v>
       </c>
-      <c r="AI20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>2.11</v>
-      </c>
       <c r="BF20" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,76 +4544,76 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="S21" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
         <v>2.01</v>
       </c>
       <c r="U21" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="V21" t="n">
         <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="X21" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.1</v>
+        <v>6.95</v>
       </c>
       <c r="AA21" t="n">
         <v>1.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG21" t="n">
         <v>3.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.45</v>
+        <v>6.35</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN21" t="n">
         <v>1.75</v>
@@ -4622,13 +4622,13 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AS21" t="n">
         <v>2.34</v>
@@ -4637,19 +4637,19 @@
         <v>3.14</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.33</v>
+        <v>3.42</v>
       </c>
       <c r="AV21" t="n">
         <v>2.38</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AX21" t="n">
         <v>1.51</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AZ21" t="n">
         <v>1.67</v>
@@ -4658,7 +4658,7 @@
         <v>2.44</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
         <v>2.25</v>
@@ -4667,10 +4667,10 @@
         <v>3.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>1.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
         <v>4.5</v>
@@ -4765,19 +4765,19 @@
         <v>2.77</v>
       </c>
       <c r="X22" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="Y22" t="n">
         <v>1.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
         <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
         <v>1.27</v>
@@ -4795,7 +4795,7 @@
         <v>3.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI22" t="n">
         <v>6.6</v>
@@ -4804,46 +4804,46 @@
         <v>1.05</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AY22" t="n">
         <v>1.32</v>
@@ -4852,22 +4852,22 @@
         <v>1.46</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="BB22" t="n">
         <v>1.22</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="BD22" t="n">
         <v>3.66</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>17.18</v>
+        <v>17</v>
       </c>
       <c r="S23" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="U23" t="n">
-        <v>12.46</v>
+        <v>13.33</v>
       </c>
       <c r="V23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.25</v>
       </c>
-      <c r="W23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="AK23" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AL23" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AM23" t="n">
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5019,52 +5019,52 @@
         <v>1.15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BA23" t="n">
         <v>6.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
         <v>2</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5332,28 +5332,28 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S25" t="n">
-        <v>4.25</v>
+        <v>4.06</v>
       </c>
       <c r="T25" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="U25" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="V25" t="n">
         <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="X25" t="n">
         <v>3</v>
@@ -5371,46 +5371,46 @@
         <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.07</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
         <v>1.83</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.62</v>
@@ -5422,10 +5422,10 @@
         <v>2.28</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.66</v>
+        <v>2.95</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="AV25" t="n">
         <v>2.14</v>
@@ -5437,28 +5437,28 @@
         <v>1.54</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="BB25" t="n">
         <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
         <v>3.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,34 +5529,34 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S26" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="U26" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V26" t="n">
         <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="X26" t="n">
         <v>2.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
         <v>7</v>
@@ -5565,40 +5565,40 @@
         <v>1.01</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
         <v>2.8</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG26" t="n">
         <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AI26" t="n">
         <v>8.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK26" t="n">
         <v>1.9</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN26" t="n">
         <v>1.3</v>
@@ -5610,13 +5610,13 @@
         <v>1.22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AT26" t="n">
         <v>2.55</v>
@@ -5628,10 +5628,10 @@
         <v>2.7</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AY26" t="n">
         <v>1.45</v>
@@ -5640,22 +5640,22 @@
         <v>2.15</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BC26" t="n">
         <v>2.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,44 +753,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -801,130 +801,130 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>8.16</v>
+        <v>1.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>8.5</v>
+        <v>1.98</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="Y2" t="n">
         <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC2" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="BF2" t="n">
         <v>1.12</v>
@@ -950,44 +950,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.44</v>
+        <v>8.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>1.98</v>
+        <v>8.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="X3" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="Y3" t="n">
         <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.59</v>
+        <v>1.05</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,16 +1112,16 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="BF3" t="n">
         <v>1.12</v>
@@ -1757,63 +1757,63 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.1</v>
+        <v>5.15</v>
       </c>
       <c r="R7" t="n">
-        <v>7.21</v>
+        <v>12.6</v>
       </c>
       <c r="S7" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="T7" t="n">
         <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="X7" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
         <v>5</v>
@@ -1825,40 +1825,40 @@
         <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AD7" t="n">
         <v>4.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
         <v>1.67</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AS7" t="n">
         <v>2.77</v>
@@ -1882,7 +1882,7 @@
         <v>2.77</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AW7" t="n">
         <v>1.65</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,171 +1945,171 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,137 +2570,137 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2742,13 +2742,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2757,60 +2757,60 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R12" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="S12" t="n">
         <v>1.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="V12" t="n">
         <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="X12" t="n">
         <v>2.32</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
         <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AB12" t="n">
         <v>1.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AD12" t="n">
         <v>4.3</v>
@@ -2822,61 +2822,61 @@
         <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AH12" t="n">
         <v>1.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.98</v>
+        <v>3.85</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AN12" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AT12" t="n">
         <v>3.14</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AV12" t="n">
         <v>2.48</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.22</v>
@@ -2888,10 +2888,10 @@
         <v>1.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
         <v>1.96</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2951,27 +2951,27 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="R13" t="n">
         <v>4.45</v>
@@ -2995,7 +2995,7 @@
         <v>2.94</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
         <v>7.5</v>
@@ -3007,28 +3007,28 @@
         <v>1.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD13" t="n">
         <v>3.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>7.38</v>
+        <v>7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK13" t="n">
         <v>1.85</v>
@@ -3049,13 +3049,13 @@
         <v>1.41</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AT13" t="n">
         <v>3.6</v>
@@ -3064,10 +3064,10 @@
         <v>2.65</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AX13" t="n">
         <v>1.38</v>
@@ -3076,22 +3076,22 @@
         <v>1.24</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BB13" t="n">
         <v>1.29</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="BD13" t="n">
         <v>3.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF13" t="n">
         <v>1.13</v>
@@ -3168,130 +3168,130 @@
         <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>5.5</v>
+        <v>6.26</v>
       </c>
       <c r="T14" t="n">
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="X14" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="AA14" t="n">
         <v>1.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AG14" t="n">
         <v>4.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.01</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AM14" t="n">
         <v>1.24</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.77</v>
+        <v>5.59</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="BA14" t="n">
         <v>1.38</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,94 +3362,94 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
         <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U15" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W15" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="X15" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI15" t="n">
         <v>6.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK15" t="n">
         <v>2</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.81</v>
+        <v>2.27</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AT15" t="n">
         <v>2.95</v>
@@ -3458,22 +3458,22 @@
         <v>3.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AY15" t="n">
         <v>1.32</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="BB15" t="n">
         <v>1.33</v>
@@ -3482,13 +3482,13 @@
         <v>2.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,171 +1945,171 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,171 +2339,171 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,34 +2733,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.25</v>
+        <v>3.59</v>
       </c>
       <c r="R12" t="n">
-        <v>8</v>
+        <v>4.45</v>
       </c>
       <c r="S12" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="X12" t="n">
-        <v>2.32</v>
+        <v>2.94</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.92</v>
+        <v>2</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY12" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,34 +2930,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
         <v>3</v>
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.59</v>
+        <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>4.45</v>
+        <v>8</v>
       </c>
       <c r="S13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.3</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG13" t="n">
-        <v>3.15</v>
+        <v>2.52</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>7</v>
+        <v>3.85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.22</v>
-      </c>
       <c r="BD13" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3139,13 +3139,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -3154,14 +3154,14 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3336,13 +3336,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -3351,14 +3351,14 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3545,17 +3545,17 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3730,48 +3730,48 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="U17" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V17" t="n">
         <v>1.25</v>
@@ -3780,10 +3780,10 @@
         <v>3.34</v>
       </c>
       <c r="X17" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Z17" t="n">
         <v>4.8</v>
@@ -3795,22 +3795,22 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AI17" t="n">
         <v>3.75</v>
@@ -3825,10 +3825,10 @@
         <v>2.25</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z18" t="n">
         <v>4.6</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.31</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
       <c r="S19" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="T19" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="W19" t="n">
-        <v>3.8</v>
+        <v>2.63</v>
       </c>
       <c r="X19" t="n">
-        <v>2.15</v>
+        <v>3.14</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.61</v>
       </c>
-      <c r="Z19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.38</v>
+        <v>1.65</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S20" t="n">
         <v>3.25</v>
@@ -4365,28 +4365,28 @@
         <v>2.8</v>
       </c>
       <c r="V20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="X20" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="Y20" t="n">
         <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AA20" t="n">
         <v>1.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD20" t="n">
         <v>3.3</v>
@@ -4395,7 +4395,7 @@
         <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
         <v>2.85</v>
@@ -4416,10 +4416,10 @@
         <v>2</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,13 +4464,13 @@
         <v>1.22</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="BD20" t="n">
         <v>3.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BF20" t="n">
         <v>1.16</v>
@@ -4550,31 +4550,31 @@
         <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>3.75</v>
+        <v>4.03</v>
       </c>
       <c r="S21" t="n">
         <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
         <v>4.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="X21" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
       <c r="AA21" t="n">
         <v>1.04</v>
@@ -4583,40 +4583,40 @@
         <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.35</v>
+        <v>6.89</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.06</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>1.85</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AU21" t="n">
         <v>3.42</v>
@@ -4646,7 +4646,7 @@
         <v>1.85</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AY21" t="n">
         <v>1.28</v>
@@ -4658,19 +4658,19 @@
         <v>2.44</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
         <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5332,16 +5332,16 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S25" t="n">
-        <v>4.06</v>
+        <v>4.16</v>
       </c>
       <c r="T25" t="n">
         <v>2.03</v>
@@ -5356,10 +5356,10 @@
         <v>2.47</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
         <v>8.699999999999999</v>
@@ -5374,76 +5374,76 @@
         <v>1.37</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AE25" t="n">
         <v>2.17</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AI25" t="n">
         <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
         <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.95</v>
+        <v>3.66</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="AV25" t="n">
         <v>2.14</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
         <v>2.33</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="BB25" t="n">
         <v>1.3</v>

--- a/jogos_2026-03-19.xlsx
+++ b/jogos_2026-03-19.xlsx
@@ -753,44 +753,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>8.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>1.98</v>
+        <v>8.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="X2" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
         <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.59</v>
+        <v>1.05</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,16 +915,16 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
         <v>1.12</v>
@@ -950,44 +950,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -998,130 +998,130 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>8.16</v>
+        <v>1.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>8.5</v>
+        <v>1.98</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC3" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="BF3" t="n">
         <v>1.12</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,171 +1945,171 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,171 +2339,171 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3936,20 +3936,20 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4112,19 +4112,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -4136,126 +4136,126 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AU19" t="n">
         <v>3.35</v>
       </c>
-      <c r="R19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,150 +4309,150 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="T20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W20" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="X20" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AX20" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4515,13 +4515,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -4530,17 +4530,17 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -4712,45 +4712,45 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
         <v>4.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="T22" t="n">
         <v>2.23</v>
@@ -4759,10 +4759,10 @@
         <v>4.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="X22" t="n">
         <v>2.85</v>
@@ -4783,19 +4783,19 @@
         <v>1.27</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
         <v>3.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AI22" t="n">
         <v>6.6</v>
@@ -4810,10 +4810,10 @@
         <v>1.95</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4822,7 +4822,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AR22" t="n">
         <v>1.87</v>
@@ -4849,7 +4849,7 @@
         <v>1.32</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BA22" t="n">
         <v>2.88</v>
@@ -4858,7 +4858,7 @@
         <v>1.22</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BD22" t="n">
         <v>3.66</v>
@@ -4938,52 +4938,52 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
         <v>17</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T23" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>13.33</v>
+        <v>13.24</v>
       </c>
       <c r="V23" t="n">
         <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="X23" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AB23" t="n">
         <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AD23" t="n">
         <v>5.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF23" t="n">
         <v>2.7</v>
@@ -4995,13 +4995,13 @@
         <v>1.67</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AL23" t="n">
         <v>1.62</v>
@@ -5010,7 +5010,7 @@
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5025,7 +5025,7 @@
         <v>1.51</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AT23" t="n">
         <v>2.27</v>
@@ -5037,10 +5037,10 @@
         <v>3.15</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AY23" t="n">
         <v>1.56</v>
@@ -5052,19 +5052,19 @@
         <v>6.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="BD23" t="n">
         <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5338,28 +5338,28 @@
         <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="S25" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="T25" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="U25" t="n">
         <v>2.95</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
         <v>2.47</v>
       </c>
       <c r="X25" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
         <v>8.699999999999999</v>
@@ -5371,25 +5371,25 @@
         <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.02</v>
@@ -5413,13 +5413,13 @@
         <v>1.32</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AR25" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AT25" t="n">
         <v>3.66</v>
@@ -5431,10 +5431,10 @@
         <v>2.14</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AY25" t="n">
         <v>1.2</v>
@@ -5449,7 +5449,7 @@
         <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="BD25" t="n">
         <v>3.1</v>
@@ -5458,7 +5458,7 @@
         <v>1.51</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5532,16 +5532,16 @@
         <v>3.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S26" t="n">
         <v>3.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="U26" t="n">
         <v>2.75</v>
@@ -5550,13 +5550,13 @@
         <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="X26" t="n">
         <v>2.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
         <v>7</v>
@@ -5568,16 +5568,16 @@
         <v>1.03</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
         <v>4</v>
@@ -5586,16 +5586,16 @@
         <v>1.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AM26" t="n">
         <v>1.36</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.37</v>
@@ -5625,7 +5625,7 @@
         <v>3.89</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AW26" t="n">
         <v>2.15</v>
@@ -5643,19 +5643,19 @@
         <v>1.79</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
